--- a/backend/data/exports/detailed_sales_report_2026-04-03.xlsx
+++ b/backend/data/exports/detailed_sales_report_2026-04-03.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>845.00</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:57:39.304821</t>
+          <t>12:15:10.116818</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:57:39.304821</t>
+          <t>22:19:34.581516</t>
         </is>
       </c>
     </row>
@@ -613,115 +613,1351 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>595.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Coldrink</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Juice</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>120.00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Paan</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>DETAILED BILLS</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Bill No</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>16:57:39.304821</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>12:15:10.116818</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>COLD071</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>JUICE</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>12:15:10.116818</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>COLD414</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>12:21:01.771563</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>COLD824</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>COCO COLA</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>12:21:01.771563</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>COLD400</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>SPRITE</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>13:01:58.886389</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>COLD954</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>SOSYO</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>13:02:13.708599</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>COLD400</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>SPRITE</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>13:02:13.708599</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>COLD062</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>SWARAS JUICE</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>13:02:13.708599</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>COLD999</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>THUMS UP(SMALL)</t>
         </is>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>16:11:19.910202</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>COLD557</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>FANTA</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>16:11:19.910202</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>16:19:31.118305</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>COLD276</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>KHARI SODA</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>16:19:31.118305</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>COLD400</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>SPRITE</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>16:21:13.969416</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>COLD091</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(BIG)</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>16:21:13.969416</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>COLD276</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>KHARI SODA</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>16:21:13.969416</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>COLD062</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>SWARAS JUICE</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>16:57:39.304821</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>16:21:13.969416</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>COLD557</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>FANTA</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>16:21:13.969416</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>OTHE742</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>WATER(SMALL)</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>16:26:56.914816</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>COLD954</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>SOSYO</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>16:26:56.914816</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>16:36:57.111170</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>OTHE425</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>WATER(BIG)</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>16:36:57.111170</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>OTHE742</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>WATER(SMALL)</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>16:36:57.111170</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>16:54:02.104521</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>COLD824</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>COCO COLA</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>16:54:02.104521</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>COLD400</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>SPRITE</t>
         </is>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="F49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>17:14:05.017993</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>17:43:39.189255</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>PAAN360</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>CHOCOLATE PAAN(SMALL)</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>17:45:31.485539</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>OTHE742</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>WATER(SMALL)</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>18:00:58.332518</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>COLD071</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>JUICE</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>18:32:59.989874</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>18:32:59.989874</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>COLD062</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>SWARAS JUICE</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>18:33:42.345211</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>COLD400</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>SPRITE</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>18:37:50.420001</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>COLD948</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>POWER UP</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>18:50:32.855816</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>COLD954</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>SOSYO</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>19:02:21.094310</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>21:05:20.125681</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>21:56:26.369396</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>COLD912</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>SabRus Jeera</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>22:19:34.581516</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>COLD557</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>FANTA</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>22:19:34.581516</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>COLD999</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>THUMS UP(SMALL)</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
@@ -733,7 +1969,7 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
